--- a/assets/sensitivity_alpha1.xlsx
+++ b/assets/sensitivity_alpha1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wonhyung64/Github/ldr_rec/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{317A6B18-1FD5-2446-BE12-19D3588C3077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C47B901-762A-A044-872A-6D622AD40588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20600" yWindow="5920" windowWidth="27700" windowHeight="16880" xr2:uid="{F32C89A8-35EC-ED44-93D9-D8E851D110CC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="26900" xr2:uid="{F32C89A8-35EC-ED44-93D9-D8E851D110CC}"/>
   </bookViews>
   <sheets>
     <sheet name="sen_gamma" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="144">
   <si>
     <t>bsarec</t>
   </si>
@@ -409,6 +409,69 @@
   <si>
     <t>alpha1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>debiased_cf_resid_only_mf_260625_211101_315247</t>
+  </si>
+  <si>
+    <t>debiased_cf_resid_only_ncf_260625_211100_772536</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_grurec_260625_211337_563379</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_sasrec_260625_211600_914293</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_tisasrec_resid_only_tisasrec_260625_211842_024240</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_fearec_260625_215212_655322</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_bsarec_260625_215918_958128</t>
+  </si>
+  <si>
+    <t>debiased_cf_resid_only_mf_260625_222844_691401</t>
+  </si>
+  <si>
+    <t>debiased_cf_resid_only_ncf_260625_223246_923649</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_grurec_260625_223258_714640</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_sasrec_260625_223600_413937</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_tisasrec_resid_only_tisasrec_260625_223651_492077</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_fearec_260625_224357_735479</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_bsarec_260625_224901_396984</t>
+  </si>
+  <si>
+    <t>debiased_cf_resid_only_mf_260630_093459_045138</t>
+  </si>
+  <si>
+    <t>debiased_cf_resid_only_ncf_260630_094102_888625</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_grurec_260630_212313_069772</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_sasrec_260630_100822_210820</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_tisasrec_resid_only_tisasrec_260626_041712_539482</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_fearec_260630_102528_597820</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_resid_only_bsarec_260630_105133_349315</t>
   </si>
 </sst>
 </file>
@@ -418,7 +481,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -438,6 +501,14 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -469,7 +540,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -477,6 +548,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE7D515-ED6B-5545-8AF2-B16B748C97E2}">
-  <dimension ref="A1:U112"/>
+  <dimension ref="A1:U131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -842,7 +916,7 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -854,16 +928,16 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>5.5300000000000002E-2</v>
+        <v>4.9500000000000002E-2</v>
       </c>
       <c r="F2">
-        <v>2.7099999999999999E-2</v>
+        <v>2.41E-2</v>
       </c>
       <c r="G2" t="s">
         <v>38</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1"/>
       <c r="O2" s="1"/>
@@ -873,7 +947,7 @@
     </row>
     <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -885,21 +959,21 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>6.3100000000000003E-2</v>
+        <v>5.5300000000000002E-2</v>
       </c>
       <c r="F3">
-        <v>3.2099999999999997E-2</v>
+        <v>2.7099999999999999E-2</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
       </c>
       <c r="H3">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -911,21 +985,21 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>5.57E-2</v>
+        <v>6.3100000000000003E-2</v>
       </c>
       <c r="F4">
-        <v>2.87E-2</v>
+        <v>3.2099999999999997E-2</v>
       </c>
       <c r="G4" t="s">
         <v>38</v>
       </c>
       <c r="H4">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -937,21 +1011,21 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>2.5100000000000001E-2</v>
+        <v>5.57E-2</v>
       </c>
       <c r="F5">
-        <v>1.34E-2</v>
+        <v>2.87E-2</v>
       </c>
       <c r="G5" t="s">
         <v>38</v>
       </c>
       <c r="H5">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -963,16 +1037,16 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>2.5000000000000001E-3</v>
+        <v>2.5100000000000001E-2</v>
       </c>
       <c r="F6">
-        <v>1.1000000000000001E-3</v>
+        <v>1.34E-2</v>
       </c>
       <c r="G6" t="s">
         <v>38</v>
       </c>
       <c r="H6">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M6" s="1"/>
       <c r="O6" s="1"/>
@@ -982,7 +1056,7 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -994,16 +1068,16 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>2.9999999999999997E-4</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="F7">
-        <v>2.0000000000000001E-4</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="M7" s="1"/>
       <c r="O7" s="1"/>
@@ -1012,7 +1086,7 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
@@ -1024,7 +1098,7 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>5.0000000000000001E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F8">
         <v>2.0000000000000001E-4</v>
@@ -1033,12 +1107,12 @@
         <v>32</v>
       </c>
       <c r="H8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
@@ -1050,21 +1124,21 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>6.9999999999999999E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F9">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="G9" t="s">
         <v>32</v>
       </c>
       <c r="H9">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -1076,16 +1150,16 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>1E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F10">
-        <v>4.0000000000000002E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="G10" t="s">
         <v>32</v>
       </c>
       <c r="H10">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="M10" s="1"/>
       <c r="O10" s="1"/>
@@ -1095,7 +1169,7 @@
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -1107,21 +1181,21 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>1.5E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="F11">
-        <v>5.9999999999999995E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="G11" t="s">
         <v>32</v>
       </c>
       <c r="H11">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -1133,16 +1207,16 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>9.06E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="F12">
-        <v>5.9400000000000001E-2</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H12">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="M12" s="1"/>
       <c r="O12" s="1"/>
@@ -1151,7 +1225,7 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -1163,21 +1237,21 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>9.2200000000000004E-2</v>
+        <v>1.5E-3</v>
       </c>
       <c r="F13">
-        <v>5.8700000000000002E-2</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H13">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -1189,16 +1263,16 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>6.6699999999999995E-2</v>
+        <v>8.3500000000000005E-2</v>
       </c>
       <c r="F14">
-        <v>3.8100000000000002E-2</v>
+        <v>5.4100000000000002E-2</v>
       </c>
       <c r="G14" t="s">
         <v>26</v>
       </c>
       <c r="H14">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1"/>
       <c r="O14" s="1"/>
@@ -1208,7 +1282,7 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -1220,21 +1294,21 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>3.4299999999999997E-2</v>
+        <v>9.06E-2</v>
       </c>
       <c r="F15">
-        <v>1.78E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="G15" t="s">
         <v>26</v>
       </c>
       <c r="H15">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -1246,21 +1320,21 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>3.0000000000000001E-3</v>
+        <v>9.2200000000000004E-2</v>
       </c>
       <c r="F16">
-        <v>1.4E-3</v>
+        <v>5.8700000000000002E-2</v>
       </c>
       <c r="G16" t="s">
         <v>26</v>
       </c>
       <c r="H16">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -1272,16 +1346,16 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>0.15</v>
+        <v>6.6699999999999995E-2</v>
       </c>
       <c r="F17">
-        <v>7.4099999999999999E-2</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H17">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M17" s="1"/>
       <c r="O17" s="1"/>
@@ -1290,7 +1364,7 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -1302,16 +1376,16 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>0.1653</v>
+        <v>3.4299999999999997E-2</v>
       </c>
       <c r="F18">
-        <v>8.1900000000000001E-2</v>
+        <v>1.78E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H18">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="M18" s="1"/>
       <c r="O18" s="1"/>
@@ -1321,7 +1395,7 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -1333,21 +1407,21 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>0.1381</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F19">
-        <v>6.8500000000000005E-2</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H19">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -1359,21 +1433,21 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>5.0999999999999997E-2</v>
+        <v>0.1361</v>
       </c>
       <c r="F20">
-        <v>2.63E-2</v>
+        <v>6.5799999999999997E-2</v>
       </c>
       <c r="G20" t="s">
         <v>20</v>
       </c>
       <c r="H20">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -1385,21 +1459,21 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>3.5999999999999999E-3</v>
+        <v>0.15</v>
       </c>
       <c r="F21">
-        <v>1.6000000000000001E-3</v>
+        <v>7.4099999999999999E-2</v>
       </c>
       <c r="G21" t="s">
         <v>20</v>
       </c>
       <c r="H21">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
@@ -1411,22 +1485,22 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>0.1676</v>
+        <v>0.1653</v>
       </c>
       <c r="F22">
-        <v>8.3699999999999997E-2</v>
+        <v>8.1900000000000001E-2</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H22">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M22" s="1"/>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
@@ -1438,21 +1512,21 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>0.1764</v>
+        <v>0.1381</v>
       </c>
       <c r="F23">
-        <v>8.9300000000000004E-2</v>
+        <v>6.8500000000000005E-2</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H23">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -1464,21 +1538,21 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>0.1492</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="F24">
-        <v>7.5499999999999998E-2</v>
+        <v>2.63E-2</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H24">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -1490,21 +1564,21 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>5.9499999999999997E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="F25">
-        <v>3.1699999999999999E-2</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="G25" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H25">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -1516,22 +1590,22 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>4.7999999999999996E-3</v>
+        <v>0.153</v>
       </c>
       <c r="F26">
-        <v>2.5999999999999999E-3</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
       <c r="H26">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
@@ -1543,13 +1617,13 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>0.1716</v>
+        <v>0.1676</v>
       </c>
       <c r="F27">
-        <v>8.6699999999999999E-2</v>
+        <v>8.3699999999999997E-2</v>
       </c>
       <c r="G27" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H27">
         <v>0.1</v>
@@ -1558,7 +1632,7 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -1570,13 +1644,13 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <v>0.18</v>
+        <v>0.1764</v>
       </c>
       <c r="F28">
-        <v>9.2700000000000005E-2</v>
+        <v>8.9300000000000004E-2</v>
       </c>
       <c r="G28" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H28">
         <v>0.3</v>
@@ -1584,7 +1658,7 @@
     </row>
     <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -1596,13 +1670,13 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>0.14899999999999999</v>
+        <v>0.1492</v>
       </c>
       <c r="F29">
-        <v>7.7100000000000002E-2</v>
+        <v>7.5499999999999998E-2</v>
       </c>
       <c r="G29" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H29">
         <v>0.5</v>
@@ -1610,7 +1684,7 @@
     </row>
     <row r="30" spans="1:21">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -1622,13 +1696,13 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>5.79E-2</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="F30">
-        <v>3.1099999999999999E-2</v>
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="G30" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H30">
         <v>0.7</v>
@@ -1636,7 +1710,7 @@
     </row>
     <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -1648,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>4.4999999999999997E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="F31">
-        <v>2.8E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="G31" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H31">
         <v>0.9</v>
@@ -1662,7 +1736,7 @@
     </row>
     <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
@@ -1674,22 +1748,22 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>0.17180000000000001</v>
+        <v>0.1605</v>
       </c>
       <c r="F32">
-        <v>8.7599999999999997E-2</v>
+        <v>7.8899999999999998E-2</v>
       </c>
       <c r="G32" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32">
         <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0.1</v>
       </c>
       <c r="M32" s="1"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
@@ -1701,22 +1775,22 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>0.17630000000000001</v>
+        <v>0.1716</v>
       </c>
       <c r="F33">
-        <v>9.1700000000000004E-2</v>
+        <v>8.6699999999999999E-2</v>
       </c>
       <c r="G33" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H33">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="M33" s="1"/>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
@@ -1728,21 +1802,21 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>0.1376</v>
+        <v>0.18</v>
       </c>
       <c r="F34">
-        <v>7.1800000000000003E-2</v>
+        <v>9.2700000000000005E-2</v>
       </c>
       <c r="G34" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -1754,21 +1828,21 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>5.74E-2</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="F35">
-        <v>3.09E-2</v>
+        <v>7.7100000000000002E-2</v>
       </c>
       <c r="G35" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H35">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B36" t="s">
         <v>2</v>
@@ -1780,63 +1854,93 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>5.1000000000000004E-3</v>
+        <v>5.79E-2</v>
       </c>
       <c r="F36">
-        <v>2.7000000000000001E-3</v>
+        <v>3.1099999999999999E-2</v>
       </c>
       <c r="G36" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H36">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="F37">
+        <v>2.8E-3</v>
+      </c>
+      <c r="G37" t="s">
+        <v>8</v>
+      </c>
+      <c r="H37">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="37" spans="1:13">
       <c r="M37" s="1"/>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" t="s">
-        <v>45</v>
-      </c>
-      <c r="F38" t="s">
-        <v>44</v>
+        <v>86</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>0.16059999999999999</v>
+      </c>
+      <c r="F38">
+        <v>7.9299999999999995E-2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
       </c>
       <c r="M38" s="1"/>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B39" t="s">
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39">
-        <v>1.6799999999999999E-2</v>
+        <v>0.17180000000000001</v>
       </c>
       <c r="F39">
-        <v>8.0000000000000002E-3</v>
+        <v>8.7599999999999997E-2</v>
       </c>
       <c r="G39" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0.1</v>
@@ -1844,25 +1948,25 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40">
-        <v>2.5600000000000001E-2</v>
+        <v>0.17630000000000001</v>
       </c>
       <c r="F40">
-        <v>1.18E-2</v>
+        <v>9.1700000000000004E-2</v>
       </c>
       <c r="G40" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>0.3</v>
@@ -1870,25 +1974,25 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41">
-        <v>3.44E-2</v>
+        <v>0.1376</v>
       </c>
       <c r="F41">
-        <v>1.6199999999999999E-2</v>
+        <v>7.1800000000000003E-2</v>
       </c>
       <c r="G41" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>0.5</v>
@@ -1897,25 +2001,25 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
-        <v>3.7999999999999999E-2</v>
+        <v>5.74E-2</v>
       </c>
       <c r="F42">
-        <v>1.7899999999999999E-2</v>
+        <v>3.09E-2</v>
       </c>
       <c r="G42" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>0.7</v>
@@ -1923,87 +2027,55 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s">
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43">
-        <v>3.5900000000000001E-2</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="F43">
-        <v>1.72E-2</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G43" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>0.9</v>
       </c>
       <c r="M43" s="1"/>
     </row>
-    <row r="44" spans="1:13">
-      <c r="A44" t="s">
-        <v>80</v>
-      </c>
-      <c r="B44" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="F44">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="G44" t="s">
-        <v>32</v>
-      </c>
-      <c r="H44">
-        <v>0.1</v>
-      </c>
-    </row>
     <row r="45" spans="1:13">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="F45">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="G45" t="s">
-        <v>32</v>
-      </c>
-      <c r="H45">
-        <v>0.3</v>
+        <v>47</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" t="s">
+        <v>44</v>
       </c>
       <c r="M45" s="1"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="B46" t="s">
         <v>2</v>
@@ -2015,21 +2087,21 @@
         <v>1</v>
       </c>
       <c r="E46">
-        <v>1.12E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="F46">
-        <v>5.0000000000000001E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="G46" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H46">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B47" t="s">
         <v>2</v>
@@ -2041,21 +2113,21 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>1.7600000000000001E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="F47">
-        <v>8.2000000000000007E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G47" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H47">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B48" t="s">
         <v>2</v>
@@ -2067,22 +2139,22 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>3.0099999999999998E-2</v>
+        <v>2.5600000000000001E-2</v>
       </c>
       <c r="F48">
-        <v>1.4E-2</v>
+        <v>1.18E-2</v>
       </c>
       <c r="G48" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H48">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="M48" s="1"/>
     </row>
     <row r="49" spans="1:19">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B49" t="s">
         <v>2</v>
@@ -2094,22 +2166,22 @@
         <v>1</v>
       </c>
       <c r="E49">
-        <v>4.82E-2</v>
+        <v>3.44E-2</v>
       </c>
       <c r="F49">
-        <v>2.35E-2</v>
+        <v>1.6199999999999999E-2</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H49">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M49" s="1"/>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B50" t="s">
         <v>2</v>
@@ -2121,21 +2193,21 @@
         <v>1</v>
       </c>
       <c r="E50">
-        <v>6.2600000000000003E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="F50">
-        <v>3.0599999999999999E-2</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="G50" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H50">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="51" spans="1:19">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B51" t="s">
         <v>2</v>
@@ -2147,21 +2219,21 @@
         <v>1</v>
       </c>
       <c r="E51">
-        <v>6.9500000000000006E-2</v>
+        <v>3.5900000000000001E-2</v>
       </c>
       <c r="F51">
-        <v>3.4200000000000001E-2</v>
+        <v>1.72E-2</v>
       </c>
       <c r="G51" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H51">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="52" spans="1:19">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="B52" t="s">
         <v>2</v>
@@ -2173,21 +2245,21 @@
         <v>1</v>
       </c>
       <c r="E52">
-        <v>6.2799999999999995E-2</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="F52">
-        <v>3.09E-2</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="G52" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H52">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B53" t="s">
         <v>2</v>
@@ -2199,16 +2271,16 @@
         <v>1</v>
       </c>
       <c r="E53">
-        <v>4.1300000000000003E-2</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="F53">
-        <v>1.9900000000000001E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G53" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H53">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="M53" s="1"/>
       <c r="O53" s="1"/>
@@ -2217,7 +2289,7 @@
     </row>
     <row r="54" spans="1:19">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B54" t="s">
         <v>2</v>
@@ -2229,21 +2301,21 @@
         <v>1</v>
       </c>
       <c r="E54">
-        <v>7.6100000000000001E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F54">
-        <v>3.6600000000000001E-2</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="G54" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H54">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="55" spans="1:19">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
         <v>2</v>
@@ -2255,21 +2327,21 @@
         <v>1</v>
       </c>
       <c r="E55">
-        <v>9.64E-2</v>
+        <v>1.12E-2</v>
       </c>
       <c r="F55">
-        <v>4.65E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G55" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H55">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56" spans="1:19">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
         <v>2</v>
@@ -2281,21 +2353,21 @@
         <v>1</v>
       </c>
       <c r="E56">
-        <v>0.1087</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="F56">
-        <v>5.28E-2</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="G56" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H56">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="57" spans="1:19">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B57" t="s">
         <v>2</v>
@@ -2307,23 +2379,23 @@
         <v>1</v>
       </c>
       <c r="E57">
-        <v>9.3600000000000003E-2</v>
+        <v>3.0099999999999998E-2</v>
       </c>
       <c r="F57">
-        <v>4.58E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G57" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H57">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="M57" s="1"/>
       <c r="O57" s="1"/>
     </row>
     <row r="58" spans="1:19">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="B58" t="s">
         <v>2</v>
@@ -2335,16 +2407,16 @@
         <v>1</v>
       </c>
       <c r="E58">
-        <v>4.65E-2</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="F58">
-        <v>2.2599999999999999E-2</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="G58" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H58">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M58" s="1"/>
       <c r="O58" s="1"/>
@@ -2353,7 +2425,7 @@
     </row>
     <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B59" t="s">
         <v>2</v>
@@ -2365,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <v>7.5300000000000006E-2</v>
+        <v>4.82E-2</v>
       </c>
       <c r="F59">
-        <v>3.6299999999999999E-2</v>
+        <v>2.35E-2</v>
       </c>
       <c r="G59" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H59">
         <v>0.1</v>
@@ -2379,7 +2451,7 @@
     </row>
     <row r="60" spans="1:19">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B60" t="s">
         <v>2</v>
@@ -2391,13 +2463,13 @@
         <v>1</v>
       </c>
       <c r="E60">
-        <v>9.7699999999999995E-2</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="F60">
-        <v>4.6899999999999997E-2</v>
+        <v>3.0599999999999999E-2</v>
       </c>
       <c r="G60" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H60">
         <v>0.3</v>
@@ -2405,7 +2477,7 @@
     </row>
     <row r="61" spans="1:19">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
         <v>2</v>
@@ -2417,13 +2489,13 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>0.1109</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="F61">
-        <v>5.3699999999999998E-2</v>
+        <v>3.4200000000000001E-2</v>
       </c>
       <c r="G61" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H61">
         <v>0.5</v>
@@ -2431,7 +2503,7 @@
     </row>
     <row r="62" spans="1:19">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s">
         <v>2</v>
@@ -2443,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="E62">
-        <v>9.9299999999999999E-2</v>
+        <v>6.2799999999999995E-2</v>
       </c>
       <c r="F62">
-        <v>4.8300000000000003E-2</v>
+        <v>3.09E-2</v>
       </c>
       <c r="G62" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H62">
         <v>0.7</v>
@@ -2457,7 +2529,7 @@
     </row>
     <row r="63" spans="1:19">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B63" t="s">
         <v>2</v>
@@ -2469,13 +2541,13 @@
         <v>1</v>
       </c>
       <c r="E63">
-        <v>4.7699999999999999E-2</v>
+        <v>4.1300000000000003E-2</v>
       </c>
       <c r="F63">
-        <v>2.3099999999999999E-2</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="G63" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H63">
         <v>0.9</v>
@@ -2487,7 +2559,7 @@
     </row>
     <row r="64" spans="1:19">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="B64" t="s">
         <v>2</v>
@@ -2499,23 +2571,23 @@
         <v>1</v>
       </c>
       <c r="E64">
-        <v>6.3399999999999998E-2</v>
+        <v>6.7100000000000007E-2</v>
       </c>
       <c r="F64">
-        <v>3.04E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="G64" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H64">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="1"/>
       <c r="O64" s="1"/>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
         <v>2</v>
@@ -2527,21 +2599,21 @@
         <v>1</v>
       </c>
       <c r="E65">
-        <v>8.0699999999999994E-2</v>
+        <v>7.6100000000000001E-2</v>
       </c>
       <c r="F65">
-        <v>3.8399999999999997E-2</v>
+        <v>3.6600000000000001E-2</v>
       </c>
       <c r="G65" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H65">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B66" t="s">
         <v>2</v>
@@ -2553,21 +2625,21 @@
         <v>1</v>
       </c>
       <c r="E66">
-        <v>9.01E-2</v>
+        <v>9.64E-2</v>
       </c>
       <c r="F66">
-        <v>4.2700000000000002E-2</v>
+        <v>4.65E-2</v>
       </c>
       <c r="G66" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H66">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
         <v>2</v>
@@ -2579,21 +2651,21 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>7.7100000000000002E-2</v>
+        <v>0.1087</v>
       </c>
       <c r="F67">
-        <v>3.73E-2</v>
+        <v>5.28E-2</v>
       </c>
       <c r="G67" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H67">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
         <v>2</v>
@@ -2605,16 +2677,16 @@
         <v>1</v>
       </c>
       <c r="E68">
-        <v>4.2599999999999999E-2</v>
+        <v>9.3600000000000003E-2</v>
       </c>
       <c r="F68">
-        <v>2.06E-2</v>
+        <v>4.58E-2</v>
       </c>
       <c r="G68" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H68">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M68" s="1"/>
       <c r="O68" s="1"/>
@@ -2624,7 +2696,7 @@
     </row>
     <row r="69" spans="1:21">
       <c r="A69" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B69" t="s">
         <v>2</v>
@@ -2636,23 +2708,23 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>4.4200000000000003E-2</v>
+        <v>4.65E-2</v>
       </c>
       <c r="F69">
-        <v>2.0899999999999998E-2</v>
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="G69" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H69">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="M69" s="1"/>
       <c r="O69" s="1"/>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
         <v>2</v>
@@ -2664,21 +2736,21 @@
         <v>1</v>
       </c>
       <c r="E70">
-        <v>5.7700000000000001E-2</v>
+        <v>6.4299999999999996E-2</v>
       </c>
       <c r="F70">
-        <v>2.6700000000000002E-2</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="G70" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70">
         <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0.3</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
         <v>2</v>
@@ -2690,21 +2762,21 @@
         <v>1</v>
       </c>
       <c r="E71">
-        <v>5.9900000000000002E-2</v>
+        <v>7.5300000000000006E-2</v>
       </c>
       <c r="F71">
-        <v>2.7799999999999998E-2</v>
+        <v>3.6299999999999999E-2</v>
       </c>
       <c r="G71" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H71">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B72" t="s">
         <v>2</v>
@@ -2716,16 +2788,16 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>4.9700000000000001E-2</v>
+        <v>9.7699999999999995E-2</v>
       </c>
       <c r="F72">
-        <v>2.3400000000000001E-2</v>
+        <v>4.6899999999999997E-2</v>
       </c>
       <c r="G72" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H72">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="M72" s="1"/>
       <c r="O72" s="1"/>
@@ -2735,7 +2807,7 @@
     </row>
     <row r="73" spans="1:21">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B73" t="s">
         <v>2</v>
@@ -2747,176 +2819,206 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>3.9199999999999999E-2</v>
+        <v>0.1109</v>
       </c>
       <c r="F73">
-        <v>1.8599999999999998E-2</v>
+        <v>5.3699999999999998E-2</v>
       </c>
       <c r="G73" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H73">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="Q73" s="1"/>
       <c r="S73" s="1"/>
     </row>
     <row r="74" spans="1:21">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" t="s">
+        <v>50</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>9.9299999999999999E-2</v>
+      </c>
+      <c r="F74">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="G74" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74">
+        <v>0.7</v>
+      </c>
       <c r="M74" s="1"/>
       <c r="O74" s="1"/>
     </row>
     <row r="75" spans="1:21">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>47</v>
-      </c>
-      <c r="D75" t="s">
-        <v>46</v>
-      </c>
-      <c r="E75" t="s">
-        <v>45</v>
-      </c>
-      <c r="F75" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="F75">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="G75" t="s">
+        <v>14</v>
+      </c>
+      <c r="H75">
+        <v>0.9</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="B76" t="s">
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
       <c r="E76">
-        <v>4.2999999999999997E-2</v>
+        <v>5.2400000000000002E-2</v>
       </c>
       <c r="F76">
-        <v>2.07E-2</v>
+        <v>2.52E-2</v>
       </c>
       <c r="G76" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H76">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="1"/>
       <c r="O76" s="1"/>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B77" t="s">
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D77">
         <v>1</v>
       </c>
       <c r="E77">
-        <v>5.8099999999999999E-2</v>
+        <v>6.3399999999999998E-2</v>
       </c>
       <c r="F77">
-        <v>2.7799999999999998E-2</v>
+        <v>3.04E-2</v>
       </c>
       <c r="G77" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H77">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B78" t="s">
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
       <c r="E78">
-        <v>6.7400000000000002E-2</v>
+        <v>8.0699999999999994E-2</v>
       </c>
       <c r="F78">
-        <v>3.2199999999999999E-2</v>
+        <v>3.8399999999999997E-2</v>
       </c>
       <c r="G78" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H78">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="B79" t="s">
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79">
-        <v>5.4899999999999997E-2</v>
+        <v>9.01E-2</v>
       </c>
       <c r="F79">
-        <v>2.7199999999999998E-2</v>
+        <v>4.2700000000000002E-2</v>
       </c>
       <c r="G79" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H79">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M79" s="1"/>
       <c r="O79" s="1"/>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B80" t="s">
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80">
-        <v>4.2500000000000003E-2</v>
+        <v>7.7100000000000002E-2</v>
       </c>
       <c r="F80">
-        <v>2.2700000000000001E-2</v>
+        <v>3.73E-2</v>
       </c>
       <c r="G80" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H80">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M80" s="1"/>
       <c r="O80" s="1"/>
@@ -2925,106 +3027,106 @@
     </row>
     <row r="81" spans="1:19">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B81" t="s">
         <v>2</v>
       </c>
       <c r="C81" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>7.4999999999999997E-3</v>
+        <v>4.2599999999999999E-2</v>
       </c>
       <c r="F81">
-        <v>3.5000000000000001E-3</v>
+        <v>2.06E-2</v>
       </c>
       <c r="G81" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H81">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="82" spans="1:19">
       <c r="A82" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="B82" t="s">
         <v>2</v>
       </c>
       <c r="C82" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82">
-        <v>8.8000000000000005E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="F82">
-        <v>4.0000000000000001E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G82" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:19">
       <c r="A83" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B83" t="s">
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>1.0800000000000001E-2</v>
+        <v>4.4200000000000003E-2</v>
       </c>
       <c r="F83">
-        <v>5.0000000000000001E-3</v>
+        <v>2.0899999999999998E-2</v>
       </c>
       <c r="G83" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="84" spans="1:19">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B84" t="s">
         <v>2</v>
       </c>
       <c r="C84" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>1.4999999999999999E-2</v>
+        <v>5.7700000000000001E-2</v>
       </c>
       <c r="F84">
-        <v>7.1000000000000004E-3</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="G84" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="M84" s="1"/>
       <c r="O84" s="1"/>
@@ -3033,109 +3135,85 @@
     </row>
     <row r="85" spans="1:19">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B85" t="s">
         <v>2</v>
       </c>
       <c r="C85" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85">
-        <v>2.93E-2</v>
+        <v>5.9900000000000002E-2</v>
       </c>
       <c r="F85">
-        <v>1.41E-2</v>
+        <v>2.7799999999999998E-2</v>
       </c>
       <c r="G85" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="Q85" s="1"/>
       <c r="S85" s="1"/>
     </row>
     <row r="86" spans="1:19">
       <c r="A86" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B86" t="s">
         <v>2</v>
       </c>
       <c r="C86" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>2.8400000000000002E-2</v>
+        <v>4.9700000000000001E-2</v>
       </c>
       <c r="F86">
-        <v>1.43E-2</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="G86" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="87" spans="1:19">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B87" t="s">
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>4.07E-2</v>
+        <v>3.9199999999999999E-2</v>
       </c>
       <c r="F87">
-        <v>2.0299999999999999E-2</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="G87" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H87">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="88" spans="1:19">
-      <c r="A88" t="s">
-        <v>29</v>
-      </c>
-      <c r="B88" t="s">
-        <v>2</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>1</v>
-      </c>
-      <c r="E88">
-        <v>5.0099999999999999E-2</v>
-      </c>
-      <c r="F88">
-        <v>2.5100000000000001E-2</v>
-      </c>
-      <c r="G88" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88">
-        <v>0.5</v>
-      </c>
       <c r="M88" s="1"/>
       <c r="O88" s="1"/>
       <c r="Q88" s="1"/>
@@ -3143,33 +3221,27 @@
     </row>
     <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="B89" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="C89" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89">
-        <v>1</v>
-      </c>
-      <c r="E89">
-        <v>5.3199999999999997E-2</v>
-      </c>
-      <c r="F89">
-        <v>2.7E-2</v>
-      </c>
-      <c r="G89" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89">
-        <v>0.7</v>
+        <v>47</v>
+      </c>
+      <c r="D89" t="s">
+        <v>46</v>
+      </c>
+      <c r="E89" t="s">
+        <v>45</v>
+      </c>
+      <c r="F89" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="90" spans="1:19">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="B90" t="s">
         <v>2</v>
@@ -3181,16 +3253,16 @@
         <v>1</v>
       </c>
       <c r="E90">
-        <v>4.3799999999999999E-2</v>
+        <v>3.44E-2</v>
       </c>
       <c r="F90">
-        <v>2.3400000000000001E-2</v>
+        <v>1.66E-2</v>
       </c>
       <c r="G90" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H90">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M90" s="1"/>
       <c r="O90" s="1"/>
@@ -3199,7 +3271,7 @@
     </row>
     <row r="91" spans="1:19">
       <c r="A91" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B91" t="s">
         <v>2</v>
@@ -3211,13 +3283,13 @@
         <v>1</v>
       </c>
       <c r="E91">
-        <v>4.2299999999999997E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="F91">
-        <v>2.0500000000000001E-2</v>
+        <v>2.07E-2</v>
       </c>
       <c r="G91" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H91">
         <v>0.1</v>
@@ -3225,7 +3297,7 @@
     </row>
     <row r="92" spans="1:19">
       <c r="A92" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
         <v>2</v>
@@ -3237,13 +3309,13 @@
         <v>1</v>
       </c>
       <c r="E92">
-        <v>5.9400000000000001E-2</v>
+        <v>5.8099999999999999E-2</v>
       </c>
       <c r="F92">
-        <v>2.86E-2</v>
+        <v>2.7799999999999998E-2</v>
       </c>
       <c r="G92" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H92">
         <v>0.3</v>
@@ -3255,7 +3327,7 @@
     </row>
     <row r="93" spans="1:19">
       <c r="A93" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B93" t="s">
         <v>2</v>
@@ -3267,13 +3339,13 @@
         <v>1</v>
       </c>
       <c r="E93">
-        <v>7.5800000000000006E-2</v>
+        <v>6.7400000000000002E-2</v>
       </c>
       <c r="F93">
-        <v>3.6700000000000003E-2</v>
+        <v>3.2199999999999999E-2</v>
       </c>
       <c r="G93" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H93">
         <v>0.5</v>
@@ -3281,7 +3353,7 @@
     </row>
     <row r="94" spans="1:19">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B94" t="s">
         <v>2</v>
@@ -3293,13 +3365,13 @@
         <v>1</v>
       </c>
       <c r="E94">
-        <v>6.6799999999999998E-2</v>
+        <v>5.4899999999999997E-2</v>
       </c>
       <c r="F94">
-        <v>3.32E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="G94" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H94">
         <v>0.7</v>
@@ -3307,7 +3379,7 @@
     </row>
     <row r="95" spans="1:19">
       <c r="A95" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B95" t="s">
         <v>2</v>
@@ -3319,13 +3391,13 @@
         <v>1</v>
       </c>
       <c r="E95">
-        <v>4.65E-2</v>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="F95">
-        <v>2.47E-2</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="G95" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H95">
         <v>0.9</v>
@@ -3337,7 +3409,7 @@
     </row>
     <row r="96" spans="1:19">
       <c r="A96" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="B96" t="s">
         <v>2</v>
@@ -3349,16 +3421,16 @@
         <v>1</v>
       </c>
       <c r="E96">
-        <v>4.1500000000000002E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F96">
-        <v>2.0199999999999999E-2</v>
+        <v>3.3E-3</v>
       </c>
       <c r="G96" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H96">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="1"/>
       <c r="O96" s="1"/>
@@ -3367,7 +3439,7 @@
     </row>
     <row r="97" spans="1:19">
       <c r="A97" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B97" t="s">
         <v>2</v>
@@ -3379,21 +3451,21 @@
         <v>1</v>
       </c>
       <c r="E97">
-        <v>5.9799999999999999E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="F97">
-        <v>2.8400000000000002E-2</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G97" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H97">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="98" spans="1:19">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B98" t="s">
         <v>2</v>
@@ -3405,21 +3477,21 @@
         <v>1</v>
       </c>
       <c r="E98">
-        <v>7.6399999999999996E-2</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="F98">
-        <v>3.6700000000000003E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="G98" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H98">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="99" spans="1:19">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B99" t="s">
         <v>2</v>
@@ -3431,21 +3503,21 @@
         <v>1</v>
       </c>
       <c r="E99">
-        <v>6.7199999999999996E-2</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="F99">
-        <v>3.32E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G99" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H99">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="100" spans="1:19">
       <c r="A100" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B100" t="s">
         <v>2</v>
@@ -3457,16 +3529,16 @@
         <v>1</v>
       </c>
       <c r="E100">
-        <v>4.7800000000000002E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="F100">
-        <v>2.4899999999999999E-2</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="G100" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H100">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M100" s="1"/>
       <c r="O100" s="1"/>
@@ -3475,7 +3547,7 @@
     </row>
     <row r="101" spans="1:19">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B101" t="s">
         <v>2</v>
@@ -3487,21 +3559,21 @@
         <v>1</v>
       </c>
       <c r="E101">
-        <v>2.0299999999999999E-2</v>
+        <v>2.93E-2</v>
       </c>
       <c r="F101">
-        <v>9.1000000000000004E-3</v>
+        <v>1.41E-2</v>
       </c>
       <c r="G101" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H101">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="102" spans="1:19">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="B102" t="s">
         <v>2</v>
@@ -3513,21 +3585,21 @@
         <v>1</v>
       </c>
       <c r="E102">
-        <v>4.0899999999999999E-2</v>
+        <v>2.1100000000000001E-2</v>
       </c>
       <c r="F102">
-        <v>1.9E-2</v>
+        <v>1.06E-2</v>
       </c>
       <c r="G102" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H102">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:19">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B103" t="s">
         <v>2</v>
@@ -3539,21 +3611,21 @@
         <v>1</v>
       </c>
       <c r="E103">
-        <v>5.9900000000000002E-2</v>
+        <v>2.8400000000000002E-2</v>
       </c>
       <c r="F103">
-        <v>2.9499999999999998E-2</v>
+        <v>1.43E-2</v>
       </c>
       <c r="G103" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H103">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="104" spans="1:19">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B104" t="s">
         <v>2</v>
@@ -3565,16 +3637,16 @@
         <v>1</v>
       </c>
       <c r="E104">
-        <v>5.6300000000000003E-2</v>
+        <v>4.07E-2</v>
       </c>
       <c r="F104">
-        <v>2.8400000000000002E-2</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="G104" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H104">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="M104" s="1"/>
       <c r="O104" s="1"/>
@@ -3583,7 +3655,7 @@
     </row>
     <row r="105" spans="1:19">
       <c r="A105" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B105" t="s">
         <v>2</v>
@@ -3595,21 +3667,21 @@
         <v>1</v>
       </c>
       <c r="E105">
-        <v>4.3799999999999999E-2</v>
+        <v>5.0099999999999999E-2</v>
       </c>
       <c r="F105">
-        <v>2.3300000000000001E-2</v>
+        <v>2.5100000000000001E-2</v>
       </c>
       <c r="G105" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H105">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="106" spans="1:19">
       <c r="A106" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B106" t="s">
         <v>2</v>
@@ -3621,21 +3693,21 @@
         <v>1</v>
       </c>
       <c r="E106">
-        <v>2.8799999999999999E-2</v>
+        <v>5.3199999999999997E-2</v>
       </c>
       <c r="F106">
-        <v>1.34E-2</v>
+        <v>2.7E-2</v>
       </c>
       <c r="G106" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H106">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="107" spans="1:19">
       <c r="A107" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B107" t="s">
         <v>2</v>
@@ -3647,21 +3719,21 @@
         <v>1</v>
       </c>
       <c r="E107">
-        <v>4.7399999999999998E-2</v>
+        <v>4.3799999999999999E-2</v>
       </c>
       <c r="F107">
-        <v>2.2100000000000002E-2</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="G107" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H107">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="108" spans="1:19">
       <c r="A108" t="s">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="B108" t="s">
         <v>2</v>
@@ -3673,16 +3745,16 @@
         <v>1</v>
       </c>
       <c r="E108">
-        <v>6.3299999999999995E-2</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="F108">
-        <v>3.0300000000000001E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="G108" t="s">
+        <v>20</v>
+      </c>
+      <c r="H108">
         <v>0</v>
-      </c>
-      <c r="H108">
-        <v>0.5</v>
       </c>
       <c r="M108" s="1"/>
       <c r="O108" s="1"/>
@@ -3691,7 +3763,7 @@
     </row>
     <row r="109" spans="1:19">
       <c r="A109" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B109" t="s">
         <v>2</v>
@@ -3703,21 +3775,21 @@
         <v>1</v>
       </c>
       <c r="E109">
-        <v>6.0699999999999997E-2</v>
+        <v>4.2299999999999997E-2</v>
       </c>
       <c r="F109">
-        <v>3.0499999999999999E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G109" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H109">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="110" spans="1:19">
       <c r="A110" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B110" t="s">
         <v>2</v>
@@ -3729,23 +3801,567 @@
         <v>1</v>
       </c>
       <c r="E110">
-        <v>4.58E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="F110">
-        <v>2.4199999999999999E-2</v>
+        <v>2.86E-2</v>
       </c>
       <c r="G110" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H110">
-        <v>0.9</v>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
+      <c r="A111" t="s">
+        <v>23</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="E111">
+        <v>7.5800000000000006E-2</v>
+      </c>
+      <c r="F111">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="G111" t="s">
+        <v>20</v>
+      </c>
+      <c r="H111">
+        <v>0.5</v>
       </c>
     </row>
     <row r="112" spans="1:19">
+      <c r="A112" t="s">
+        <v>22</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1</v>
+      </c>
+      <c r="D112">
+        <v>1</v>
+      </c>
+      <c r="E112">
+        <v>6.6799999999999998E-2</v>
+      </c>
+      <c r="F112">
+        <v>3.32E-2</v>
+      </c>
+      <c r="G112" t="s">
+        <v>20</v>
+      </c>
+      <c r="H112">
+        <v>0.7</v>
+      </c>
       <c r="M112" s="1"/>
       <c r="O112" s="1"/>
       <c r="Q112" s="1"/>
       <c r="S112" s="1"/>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>21</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1</v>
+      </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
+      <c r="E113">
+        <v>4.65E-2</v>
+      </c>
+      <c r="F113">
+        <v>2.47E-2</v>
+      </c>
+      <c r="G113" t="s">
+        <v>20</v>
+      </c>
+      <c r="H113">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D114" s="3">
+        <v>1</v>
+      </c>
+      <c r="E114" s="3">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="F114" s="3">
+        <v>1.54E-2</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>19</v>
+      </c>
+      <c r="B115" t="s">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="F115">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="G115" t="s">
+        <v>14</v>
+      </c>
+      <c r="H115">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>18</v>
+      </c>
+      <c r="B116" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+      <c r="E116">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="F116">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="G116" t="s">
+        <v>14</v>
+      </c>
+      <c r="H116">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>17</v>
+      </c>
+      <c r="B117" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+      <c r="E117">
+        <v>7.6399999999999996E-2</v>
+      </c>
+      <c r="F117">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="G117" t="s">
+        <v>14</v>
+      </c>
+      <c r="H117">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>16</v>
+      </c>
+      <c r="B118" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>6.7199999999999996E-2</v>
+      </c>
+      <c r="F118">
+        <v>3.32E-2</v>
+      </c>
+      <c r="G118" t="s">
+        <v>14</v>
+      </c>
+      <c r="H118">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>2</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="E119">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="F119">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="G119" t="s">
+        <v>14</v>
+      </c>
+      <c r="H119">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>142</v>
+      </c>
+      <c r="B120" t="s">
+        <v>2</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="F120">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="G120" t="s">
+        <v>8</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>13</v>
+      </c>
+      <c r="B121" t="s">
+        <v>2</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="E121">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="F121">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="G121" t="s">
+        <v>8</v>
+      </c>
+      <c r="H121">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122" t="s">
+        <v>2</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="F122">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G122" t="s">
+        <v>8</v>
+      </c>
+      <c r="H122">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" t="s">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="F123">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="G123" t="s">
+        <v>8</v>
+      </c>
+      <c r="H123">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>10</v>
+      </c>
+      <c r="B124" t="s">
+        <v>2</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="F124">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="G124" t="s">
+        <v>8</v>
+      </c>
+      <c r="H124">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>9</v>
+      </c>
+      <c r="B125" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+      <c r="E125">
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="F125">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="G125" t="s">
+        <v>8</v>
+      </c>
+      <c r="H125">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>143</v>
+      </c>
+      <c r="B126" t="s">
+        <v>2</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="E126">
+        <v>2.29E-2</v>
+      </c>
+      <c r="F126">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G126" t="s">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B127" t="s">
+        <v>2</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="F127">
+        <v>1.34E-2</v>
+      </c>
+      <c r="G127" t="s">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" t="s">
+        <v>2</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="F128">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="G128" t="s">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>5</v>
+      </c>
+      <c r="B129" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129">
+        <v>6.3299999999999995E-2</v>
+      </c>
+      <c r="F129">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="G129" t="s">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>4</v>
+      </c>
+      <c r="B130" t="s">
+        <v>2</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>6.0699999999999997E-2</v>
+      </c>
+      <c r="F130">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="G130" t="s">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>3</v>
+      </c>
+      <c r="B131" t="s">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>4.58E-2</v>
+      </c>
+      <c r="F131">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="G131" t="s">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0.9</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/assets/sensitivity_alpha1.xlsx
+++ b/assets/sensitivity_alpha1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wonhyung64/Github/ldr_rec/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C47B901-762A-A044-872A-6D622AD40588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DD9A1A-A9FF-834D-986D-9BAB179C7B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="26900" xr2:uid="{F32C89A8-35EC-ED44-93D9-D8E851D110CC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="165">
   <si>
     <t>bsarec</t>
   </si>
@@ -472,6 +472,69 @@
   </si>
   <si>
     <t>debiased_seq_rec_resid_only_bsarec_260630_105133_349315</t>
+  </si>
+  <si>
+    <t>debiased_cf_weighted_mf_260715_122347_928386</t>
+  </si>
+  <si>
+    <t>debiased_cf_weighted_ncf_260715_122344_504462</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_grurec_260715_122353_268451</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_sasrec_260715_122358_726595</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_tisasrec_weighted_tisasrec_260715_123148_123795</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_fearec_260715_123153_291954</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_bsarec_260715_123158_358801</t>
+  </si>
+  <si>
+    <t>debiased_cf_weighted_mf_260715_123203_394497</t>
+  </si>
+  <si>
+    <t>debiased_cf_weighted_ncf_260715_124255_057376</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_grurec_260715_124300_071665</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_sasrec_260715_124304_559171</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_tisasrec_weighted_tisasrec_260715_153052_345592</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_fearec_260715_133227_094839</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_bsarec_260715_133230_085363</t>
+  </si>
+  <si>
+    <t>debiased_cf_weighted_mf_260715_133235_103059</t>
+  </si>
+  <si>
+    <t>debiased_cf_weighted_ncf_260715_133240_234713</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_grurec_260715_135033_997642</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_sasrec_260715_135038_721468</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_tisasrec_weighted_tisasrec_260715_135044_359445</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_fearec_260715_135049_417746</t>
+  </si>
+  <si>
+    <t>debiased_seq_rec_weighted_bsarec_260715_143302_326939</t>
   </si>
 </sst>
 </file>
@@ -888,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE7D515-ED6B-5545-8AF2-B16B748C97E2}">
-  <dimension ref="A1:U131"/>
+  <dimension ref="A1:U152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -1086,7 +1149,7 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
@@ -1098,21 +1161,21 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="F8">
-        <v>2.0000000000000001E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
@@ -1133,12 +1196,12 @@
         <v>32</v>
       </c>
       <c r="H9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -1150,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>5.0000000000000001E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F10">
         <v>2.0000000000000001E-4</v>
@@ -1159,7 +1222,7 @@
         <v>32</v>
       </c>
       <c r="H10">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="M10" s="1"/>
       <c r="O10" s="1"/>
@@ -1169,7 +1232,7 @@
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -1181,21 +1244,21 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F11">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="G11" t="s">
         <v>32</v>
       </c>
       <c r="H11">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -1207,16 +1270,16 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>1E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="F12">
-        <v>4.0000000000000002E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="G12" t="s">
         <v>32</v>
       </c>
       <c r="H12">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M12" s="1"/>
       <c r="O12" s="1"/>
@@ -1225,7 +1288,7 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -1237,21 +1300,21 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1.5E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="F13">
-        <v>5.9999999999999995E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
       </c>
       <c r="H13">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -1263,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>8.3500000000000005E-2</v>
+        <v>1.5E-3</v>
       </c>
       <c r="F14">
-        <v>5.4100000000000002E-2</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M14" s="1"/>
       <c r="O14" s="1"/>
@@ -1282,7 +1345,7 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -1294,21 +1357,21 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>9.06E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="F15">
-        <v>5.9400000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H15">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -1320,21 +1383,21 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>9.2200000000000004E-2</v>
+        <v>8.3500000000000005E-2</v>
       </c>
       <c r="F16">
-        <v>5.8700000000000002E-2</v>
+        <v>5.4100000000000002E-2</v>
       </c>
       <c r="G16" t="s">
         <v>26</v>
       </c>
       <c r="H16">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -1346,16 +1409,16 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>6.6699999999999995E-2</v>
+        <v>9.06E-2</v>
       </c>
       <c r="F17">
-        <v>3.8100000000000002E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="G17" t="s">
         <v>26</v>
       </c>
       <c r="H17">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="M17" s="1"/>
       <c r="O17" s="1"/>
@@ -1364,7 +1427,7 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -1376,16 +1439,16 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>3.4299999999999997E-2</v>
+        <v>9.2200000000000004E-2</v>
       </c>
       <c r="F18">
-        <v>1.78E-2</v>
+        <v>5.8700000000000002E-2</v>
       </c>
       <c r="G18" t="s">
         <v>26</v>
       </c>
       <c r="H18">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="M18" s="1"/>
       <c r="O18" s="1"/>
@@ -1395,7 +1458,7 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -1407,21 +1470,21 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>3.0000000000000001E-3</v>
+        <v>6.6699999999999995E-2</v>
       </c>
       <c r="F19">
-        <v>1.4E-3</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="G19" t="s">
         <v>26</v>
       </c>
       <c r="H19">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -1433,21 +1496,21 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>0.1361</v>
+        <v>3.4299999999999997E-2</v>
       </c>
       <c r="F20">
-        <v>6.5799999999999997E-2</v>
+        <v>1.78E-2</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -1459,21 +1522,21 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>0.15</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F21">
-        <v>7.4099999999999999E-2</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H21">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
@@ -1485,22 +1548,22 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>0.1653</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="F22">
-        <v>8.1900000000000001E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H22">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="M22" s="1"/>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
@@ -1512,21 +1575,21 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>0.1381</v>
+        <v>0.1361</v>
       </c>
       <c r="F23">
-        <v>6.8500000000000005E-2</v>
+        <v>6.5799999999999997E-2</v>
       </c>
       <c r="G23" t="s">
         <v>20</v>
       </c>
       <c r="H23">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -1538,21 +1601,21 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>5.0999999999999997E-2</v>
+        <v>0.15</v>
       </c>
       <c r="F24">
-        <v>2.63E-2</v>
+        <v>7.4099999999999999E-2</v>
       </c>
       <c r="G24" t="s">
         <v>20</v>
       </c>
       <c r="H24">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -1564,21 +1627,21 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>3.5999999999999999E-3</v>
+        <v>0.1653</v>
       </c>
       <c r="F25">
-        <v>1.6000000000000001E-3</v>
+        <v>8.1900000000000001E-2</v>
       </c>
       <c r="G25" t="s">
         <v>20</v>
       </c>
       <c r="H25">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -1590,22 +1653,22 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>0.153</v>
+        <v>0.1381</v>
       </c>
       <c r="F26">
-        <v>7.5200000000000003E-2</v>
+        <v>6.8500000000000005E-2</v>
       </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
@@ -1617,22 +1680,22 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>0.1676</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="F27">
-        <v>8.3699999999999997E-2</v>
+        <v>2.63E-2</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H27">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="M27" s="1"/>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -1644,21 +1707,21 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <v>0.1764</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="F28">
-        <v>8.9300000000000004E-2</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="G28" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H28">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -1670,21 +1733,21 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>0.1492</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="F29">
-        <v>7.5499999999999998E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H29">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -1696,21 +1759,21 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>5.9499999999999997E-2</v>
+        <v>0.153</v>
       </c>
       <c r="F30">
-        <v>3.1699999999999999E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
       </c>
       <c r="H30">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -1722,21 +1785,21 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>4.7999999999999996E-3</v>
+        <v>0.1676</v>
       </c>
       <c r="F31">
-        <v>2.5999999999999999E-3</v>
+        <v>8.3699999999999997E-2</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
       </c>
       <c r="H31">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
@@ -1748,22 +1811,22 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>0.1605</v>
+        <v>0.1764</v>
       </c>
       <c r="F32">
-        <v>7.8899999999999998E-2</v>
+        <v>8.9300000000000004E-2</v>
       </c>
       <c r="G32" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M32" s="1"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
@@ -1775,22 +1838,22 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>0.1716</v>
+        <v>0.1492</v>
       </c>
       <c r="F33">
-        <v>8.6699999999999999E-2</v>
+        <v>7.5499999999999998E-2</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H33">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M33" s="1"/>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
@@ -1802,21 +1865,21 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>0.18</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="F34">
-        <v>9.2700000000000005E-2</v>
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="G34" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H34">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -1828,21 +1891,21 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>0.14899999999999999</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="F35">
-        <v>7.7100000000000002E-2</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="G35" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H35">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="B36" t="s">
         <v>2</v>
@@ -1854,21 +1917,21 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>5.79E-2</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="F36">
-        <v>3.1099999999999999E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="G36" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H36">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s">
         <v>2</v>
@@ -1880,22 +1943,22 @@
         <v>1</v>
       </c>
       <c r="E37">
-        <v>4.4999999999999997E-3</v>
+        <v>0.1605</v>
       </c>
       <c r="F37">
-        <v>2.8E-3</v>
+        <v>7.8899999999999998E-2</v>
       </c>
       <c r="G37" t="s">
         <v>8</v>
       </c>
       <c r="H37">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M37" s="1"/>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="B38" t="s">
         <v>2</v>
@@ -1907,22 +1970,22 @@
         <v>1</v>
       </c>
       <c r="E38">
-        <v>0.16059999999999999</v>
+        <v>0.1716</v>
       </c>
       <c r="F38">
-        <v>7.9299999999999995E-2</v>
+        <v>8.6699999999999999E-2</v>
       </c>
       <c r="G38" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M38" s="1"/>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B39" t="s">
         <v>2</v>
@@ -1934,21 +1997,21 @@
         <v>1</v>
       </c>
       <c r="E39">
-        <v>0.17180000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="F39">
-        <v>8.7599999999999997E-2</v>
+        <v>9.2700000000000005E-2</v>
       </c>
       <c r="G39" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H39">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
         <v>2</v>
@@ -1960,21 +2023,21 @@
         <v>1</v>
       </c>
       <c r="E40">
-        <v>0.17630000000000001</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="F40">
-        <v>9.1700000000000004E-2</v>
+        <v>7.7100000000000002E-2</v>
       </c>
       <c r="G40" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H40">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s">
         <v>2</v>
@@ -1986,22 +2049,22 @@
         <v>1</v>
       </c>
       <c r="E41">
-        <v>0.1376</v>
+        <v>5.79E-2</v>
       </c>
       <c r="F41">
-        <v>7.1800000000000003E-2</v>
+        <v>3.1099999999999999E-2</v>
       </c>
       <c r="G41" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H41">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M41" s="1"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
         <v>2</v>
@@ -2013,21 +2076,21 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>5.74E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="F42">
-        <v>3.09E-2</v>
+        <v>2.8E-3</v>
       </c>
       <c r="G42" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H42">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="B43" t="s">
         <v>2</v>
@@ -2039,227 +2102,227 @@
         <v>1</v>
       </c>
       <c r="E43">
-        <v>5.1000000000000004E-3</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="F43">
-        <v>2.7000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="G43" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>0.16059999999999999</v>
+      </c>
+      <c r="F44">
+        <v>7.9299999999999995E-2</v>
+      </c>
+      <c r="G44" t="s">
         <v>0</v>
       </c>
-      <c r="H43">
-        <v>0.9</v>
-      </c>
-      <c r="M43" s="1"/>
+      <c r="H44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" t="s">
-        <v>46</v>
-      </c>
-      <c r="E45" t="s">
-        <v>45</v>
-      </c>
-      <c r="F45" t="s">
-        <v>44</v>
+        <v>86</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>0.17180000000000001</v>
+      </c>
+      <c r="F45">
+        <v>8.7599999999999997E-2</v>
+      </c>
+      <c r="G45" t="s">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0.1</v>
       </c>
       <c r="M45" s="1"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="B46" t="s">
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46">
-        <v>1.3100000000000001E-2</v>
+        <v>0.17630000000000001</v>
       </c>
       <c r="F46">
-        <v>6.1999999999999998E-3</v>
+        <v>9.1700000000000004E-2</v>
       </c>
       <c r="G46" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B47" t="s">
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47">
-        <v>1.6799999999999999E-2</v>
+        <v>0.1376</v>
       </c>
       <c r="F47">
-        <v>8.0000000000000002E-3</v>
+        <v>7.1800000000000003E-2</v>
       </c>
       <c r="G47" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48">
-        <v>2.5600000000000001E-2</v>
+        <v>5.74E-2</v>
       </c>
       <c r="F48">
-        <v>1.18E-2</v>
+        <v>3.09E-2</v>
       </c>
       <c r="G48" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="M48" s="1"/>
     </row>
     <row r="49" spans="1:19">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B49" t="s">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D49">
         <v>1</v>
       </c>
       <c r="E49">
-        <v>3.44E-2</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="F49">
-        <v>1.6199999999999999E-2</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G49" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="M49" s="1"/>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="B50" t="s">
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>3.7999999999999999E-2</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="F50">
-        <v>1.7899999999999999E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="G50" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19">
-      <c r="A51" t="s">
-        <v>81</v>
-      </c>
-      <c r="B51" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51">
-        <v>3.5900000000000001E-2</v>
-      </c>
-      <c r="F51">
-        <v>1.72E-2</v>
-      </c>
-      <c r="G51" t="s">
-        <v>38</v>
-      </c>
-      <c r="H51">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:19">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
-        <v>4.5999999999999999E-3</v>
-      </c>
-      <c r="F52">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="G52" t="s">
-        <v>32</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="D52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" t="s">
+        <v>45</v>
+      </c>
+      <c r="F52" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="B53" t="s">
         <v>2</v>
@@ -2271,16 +2334,16 @@
         <v>1</v>
       </c>
       <c r="E53">
-        <v>5.4999999999999997E-3</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="F53">
-        <v>2.5000000000000001E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="G53" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H53">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="1"/>
       <c r="O53" s="1"/>
@@ -2289,7 +2352,7 @@
     </row>
     <row r="54" spans="1:19">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B54" t="s">
         <v>2</v>
@@ -2301,21 +2364,21 @@
         <v>1</v>
       </c>
       <c r="E54">
-        <v>7.0000000000000001E-3</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="F54">
-        <v>3.2000000000000002E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G54" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H54">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="55" spans="1:19">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B55" t="s">
         <v>2</v>
@@ -2327,21 +2390,21 @@
         <v>1</v>
       </c>
       <c r="E55">
-        <v>1.12E-2</v>
+        <v>2.5600000000000001E-2</v>
       </c>
       <c r="F55">
-        <v>5.0000000000000001E-3</v>
+        <v>1.18E-2</v>
       </c>
       <c r="G55" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H55">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="56" spans="1:19">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B56" t="s">
         <v>2</v>
@@ -2353,21 +2416,21 @@
         <v>1</v>
       </c>
       <c r="E56">
-        <v>1.7600000000000001E-2</v>
+        <v>3.44E-2</v>
       </c>
       <c r="F56">
-        <v>8.2000000000000007E-3</v>
+        <v>1.6199999999999999E-2</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H56">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="57" spans="1:19">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
         <v>2</v>
@@ -2379,23 +2442,23 @@
         <v>1</v>
       </c>
       <c r="E57">
-        <v>3.0099999999999998E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="F57">
-        <v>1.4E-2</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="G57" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H57">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M57" s="1"/>
       <c r="O57" s="1"/>
     </row>
     <row r="58" spans="1:19">
       <c r="A58" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="B58" t="s">
         <v>2</v>
@@ -2407,16 +2470,16 @@
         <v>1</v>
       </c>
       <c r="E58">
-        <v>4.1099999999999998E-2</v>
+        <v>3.5900000000000001E-2</v>
       </c>
       <c r="F58">
-        <v>1.9900000000000001E-2</v>
+        <v>1.72E-2</v>
       </c>
       <c r="G58" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M58" s="1"/>
       <c r="O58" s="1"/>
@@ -2425,7 +2488,7 @@
     </row>
     <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="B59" t="s">
         <v>2</v>
@@ -2437,21 +2500,21 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <v>4.82E-2</v>
+        <v>3.4799999999999998E-2</v>
       </c>
       <c r="F59">
-        <v>2.35E-2</v>
+        <v>1.66E-2</v>
       </c>
       <c r="G59" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H59">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:19">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="B60" t="s">
         <v>2</v>
@@ -2463,21 +2526,21 @@
         <v>1</v>
       </c>
       <c r="E60">
-        <v>6.2600000000000003E-2</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="F60">
-        <v>3.0599999999999999E-2</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="G60" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H60">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:19">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B61" t="s">
         <v>2</v>
@@ -2489,21 +2552,21 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>6.9500000000000006E-2</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="F61">
-        <v>3.4200000000000001E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G61" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H61">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="62" spans="1:19">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
         <v>2</v>
@@ -2515,21 +2578,21 @@
         <v>1</v>
       </c>
       <c r="E62">
-        <v>6.2799999999999995E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F62">
-        <v>3.09E-2</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="G62" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H62">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="63" spans="1:19">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B63" t="s">
         <v>2</v>
@@ -2541,16 +2604,16 @@
         <v>1</v>
       </c>
       <c r="E63">
-        <v>4.1300000000000003E-2</v>
+        <v>1.12E-2</v>
       </c>
       <c r="F63">
-        <v>1.9900000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G63" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H63">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="M63" s="1"/>
       <c r="O63" s="1"/>
@@ -2559,7 +2622,7 @@
     </row>
     <row r="64" spans="1:19">
       <c r="A64" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="B64" t="s">
         <v>2</v>
@@ -2571,23 +2634,23 @@
         <v>1</v>
       </c>
       <c r="E64">
-        <v>6.7100000000000007E-2</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="F64">
-        <v>3.2399999999999998E-2</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="G64" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M64" s="1"/>
       <c r="O64" s="1"/>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s">
         <v>2</v>
@@ -2599,21 +2662,21 @@
         <v>1</v>
       </c>
       <c r="E65">
-        <v>7.6100000000000001E-2</v>
+        <v>3.0099999999999998E-2</v>
       </c>
       <c r="F65">
-        <v>3.6600000000000001E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G65" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H65">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="B66" t="s">
         <v>2</v>
@@ -2625,21 +2688,21 @@
         <v>1</v>
       </c>
       <c r="E66">
-        <v>9.64E-2</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="F66">
-        <v>4.65E-2</v>
+        <v>1.67E-2</v>
       </c>
       <c r="G66" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H66">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="B67" t="s">
         <v>2</v>
@@ -2651,21 +2714,21 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>0.1087</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="F67">
-        <v>5.28E-2</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="G67" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B68" t="s">
         <v>2</v>
@@ -2677,16 +2740,16 @@
         <v>1</v>
       </c>
       <c r="E68">
-        <v>9.3600000000000003E-2</v>
+        <v>4.82E-2</v>
       </c>
       <c r="F68">
-        <v>4.58E-2</v>
+        <v>2.35E-2</v>
       </c>
       <c r="G68" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H68">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="M68" s="1"/>
       <c r="O68" s="1"/>
@@ -2696,7 +2759,7 @@
     </row>
     <row r="69" spans="1:21">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B69" t="s">
         <v>2</v>
@@ -2708,23 +2771,23 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>4.65E-2</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="F69">
-        <v>2.2599999999999999E-2</v>
+        <v>3.0599999999999999E-2</v>
       </c>
       <c r="G69" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H69">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="M69" s="1"/>
       <c r="O69" s="1"/>
     </row>
     <row r="70" spans="1:21">
       <c r="A70" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="B70" t="s">
         <v>2</v>
@@ -2736,21 +2799,21 @@
         <v>1</v>
       </c>
       <c r="E70">
-        <v>6.4299999999999996E-2</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="F70">
-        <v>3.0800000000000001E-2</v>
+        <v>3.4200000000000001E-2</v>
       </c>
       <c r="G70" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
         <v>2</v>
@@ -2762,21 +2825,21 @@
         <v>1</v>
       </c>
       <c r="E71">
-        <v>7.5300000000000006E-2</v>
+        <v>6.2799999999999995E-2</v>
       </c>
       <c r="F71">
-        <v>3.6299999999999999E-2</v>
+        <v>3.09E-2</v>
       </c>
       <c r="G71" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H71">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
         <v>2</v>
@@ -2788,16 +2851,16 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>9.7699999999999995E-2</v>
+        <v>4.1300000000000003E-2</v>
       </c>
       <c r="F72">
-        <v>4.6899999999999997E-2</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="G72" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H72">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="M72" s="1"/>
       <c r="O72" s="1"/>
@@ -2807,7 +2870,7 @@
     </row>
     <row r="73" spans="1:21">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="B73" t="s">
         <v>2</v>
@@ -2819,23 +2882,23 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>0.1109</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="F73">
-        <v>5.3699999999999998E-2</v>
+        <v>1.66E-2</v>
       </c>
       <c r="G73" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H73">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="1"/>
       <c r="S73" s="1"/>
     </row>
     <row r="74" spans="1:21">
       <c r="A74" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B74" t="s">
         <v>2</v>
@@ -2847,23 +2910,23 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>9.9299999999999999E-2</v>
+        <v>6.7100000000000007E-2</v>
       </c>
       <c r="F74">
-        <v>4.8300000000000003E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="G74" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H74">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M74" s="1"/>
       <c r="O74" s="1"/>
     </row>
     <row r="75" spans="1:21">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B75" t="s">
         <v>2</v>
@@ -2875,21 +2938,21 @@
         <v>1</v>
       </c>
       <c r="E75">
-        <v>4.7699999999999999E-2</v>
+        <v>7.6100000000000001E-2</v>
       </c>
       <c r="F75">
-        <v>2.3099999999999999E-2</v>
+        <v>3.6600000000000001E-2</v>
       </c>
       <c r="G75" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H75">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="B76" t="s">
         <v>2</v>
@@ -2901,23 +2964,23 @@
         <v>1</v>
       </c>
       <c r="E76">
-        <v>5.2400000000000002E-2</v>
+        <v>9.64E-2</v>
       </c>
       <c r="F76">
-        <v>2.52E-2</v>
+        <v>4.65E-2</v>
       </c>
       <c r="G76" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M76" s="1"/>
       <c r="O76" s="1"/>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B77" t="s">
         <v>2</v>
@@ -2929,21 +2992,21 @@
         <v>1</v>
       </c>
       <c r="E77">
-        <v>6.3399999999999998E-2</v>
+        <v>0.1087</v>
       </c>
       <c r="F77">
-        <v>3.04E-2</v>
+        <v>5.28E-2</v>
       </c>
       <c r="G77" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H77">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B78" t="s">
         <v>2</v>
@@ -2955,21 +3018,21 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>8.0699999999999994E-2</v>
+        <v>9.3600000000000003E-2</v>
       </c>
       <c r="F78">
-        <v>3.8399999999999997E-2</v>
+        <v>4.58E-2</v>
       </c>
       <c r="G78" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H78">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B79" t="s">
         <v>2</v>
@@ -2981,23 +3044,23 @@
         <v>1</v>
       </c>
       <c r="E79">
-        <v>9.01E-2</v>
+        <v>4.65E-2</v>
       </c>
       <c r="F79">
-        <v>4.2700000000000002E-2</v>
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="G79" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H79">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="M79" s="1"/>
       <c r="O79" s="1"/>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="B80" t="s">
         <v>2</v>
@@ -3009,16 +3072,16 @@
         <v>1</v>
       </c>
       <c r="E80">
-        <v>7.7100000000000002E-2</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="F80">
-        <v>3.73E-2</v>
+        <v>1.66E-2</v>
       </c>
       <c r="G80" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H80">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M80" s="1"/>
       <c r="O80" s="1"/>
@@ -3027,7 +3090,7 @@
     </row>
     <row r="81" spans="1:19">
       <c r="A81" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="B81" t="s">
         <v>2</v>
@@ -3039,21 +3102,21 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>4.2599999999999999E-2</v>
+        <v>6.4299999999999996E-2</v>
       </c>
       <c r="F81">
-        <v>2.06E-2</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="G81" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H81">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:19">
       <c r="A82" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="B82" t="s">
         <v>2</v>
@@ -3065,21 +3128,21 @@
         <v>1</v>
       </c>
       <c r="E82">
-        <v>1E-3</v>
+        <v>7.5300000000000006E-2</v>
       </c>
       <c r="F82">
-        <v>4.0000000000000002E-4</v>
+        <v>3.6299999999999999E-2</v>
       </c>
       <c r="G82" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="83" spans="1:19">
       <c r="A83" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B83" t="s">
         <v>2</v>
@@ -3091,21 +3154,21 @@
         <v>1</v>
       </c>
       <c r="E83">
-        <v>4.4200000000000003E-2</v>
+        <v>9.7699999999999995E-2</v>
       </c>
       <c r="F83">
-        <v>2.0899999999999998E-2</v>
+        <v>4.6899999999999997E-2</v>
       </c>
       <c r="G83" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H83">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="84" spans="1:19">
       <c r="A84" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B84" t="s">
         <v>2</v>
@@ -3117,16 +3180,16 @@
         <v>1</v>
       </c>
       <c r="E84">
-        <v>5.7700000000000001E-2</v>
+        <v>0.1109</v>
       </c>
       <c r="F84">
-        <v>2.6700000000000002E-2</v>
+        <v>5.3699999999999998E-2</v>
       </c>
       <c r="G84" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H84">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M84" s="1"/>
       <c r="O84" s="1"/>
@@ -3135,7 +3198,7 @@
     </row>
     <row r="85" spans="1:19">
       <c r="A85" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B85" t="s">
         <v>2</v>
@@ -3147,23 +3210,23 @@
         <v>1</v>
       </c>
       <c r="E85">
-        <v>5.9900000000000002E-2</v>
+        <v>9.9299999999999999E-2</v>
       </c>
       <c r="F85">
-        <v>2.7799999999999998E-2</v>
+        <v>4.8300000000000003E-2</v>
       </c>
       <c r="G85" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H85">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q85" s="1"/>
       <c r="S85" s="1"/>
     </row>
     <row r="86" spans="1:19">
       <c r="A86" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B86" t="s">
         <v>2</v>
@@ -3175,21 +3238,21 @@
         <v>1</v>
       </c>
       <c r="E86">
-        <v>4.9700000000000001E-2</v>
+        <v>4.7699999999999999E-2</v>
       </c>
       <c r="F86">
-        <v>2.3400000000000001E-2</v>
+        <v>2.3099999999999999E-2</v>
       </c>
       <c r="G86" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H86">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="87" spans="1:19">
       <c r="A87" t="s">
-        <v>51</v>
+        <v>155</v>
       </c>
       <c r="B87" t="s">
         <v>2</v>
@@ -3201,19 +3264,43 @@
         <v>1</v>
       </c>
       <c r="E87">
-        <v>3.9199999999999999E-2</v>
+        <v>3.4299999999999997E-2</v>
       </c>
       <c r="F87">
-        <v>1.8599999999999998E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="G87" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19">
+      <c r="A88" t="s">
+        <v>135</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>5.2400000000000002E-2</v>
+      </c>
+      <c r="F88">
+        <v>2.52E-2</v>
+      </c>
+      <c r="G88" t="s">
+        <v>8</v>
+      </c>
+      <c r="H88">
         <v>0</v>
       </c>
-      <c r="H87">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19">
       <c r="M88" s="1"/>
       <c r="O88" s="1"/>
       <c r="Q88" s="1"/>
@@ -3221,48 +3308,54 @@
     </row>
     <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C89" t="s">
-        <v>47</v>
-      </c>
-      <c r="D89" t="s">
-        <v>46</v>
-      </c>
-      <c r="E89" t="s">
-        <v>45</v>
-      </c>
-      <c r="F89" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>6.3399999999999998E-2</v>
+      </c>
+      <c r="F89">
+        <v>3.04E-2</v>
+      </c>
+      <c r="G89" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89">
+        <v>0.1</v>
       </c>
     </row>
     <row r="90" spans="1:19">
       <c r="A90" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="B90" t="s">
         <v>2</v>
       </c>
       <c r="C90" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90">
-        <v>3.44E-2</v>
+        <v>8.0699999999999994E-2</v>
       </c>
       <c r="F90">
-        <v>1.66E-2</v>
+        <v>3.8399999999999997E-2</v>
       </c>
       <c r="G90" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M90" s="1"/>
       <c r="O90" s="1"/>
@@ -3271,54 +3364,54 @@
     </row>
     <row r="91" spans="1:19">
       <c r="A91" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B91" t="s">
         <v>2</v>
       </c>
       <c r="C91" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91">
-        <v>4.2999999999999997E-2</v>
+        <v>9.01E-2</v>
       </c>
       <c r="F91">
-        <v>2.07E-2</v>
+        <v>4.2700000000000002E-2</v>
       </c>
       <c r="G91" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H91">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="92" spans="1:19">
       <c r="A92" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B92" t="s">
         <v>2</v>
       </c>
       <c r="C92" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92">
-        <v>5.8099999999999999E-2</v>
+        <v>7.7100000000000002E-2</v>
       </c>
       <c r="F92">
-        <v>2.7799999999999998E-2</v>
+        <v>3.73E-2</v>
       </c>
       <c r="G92" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H92">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="M92" s="1"/>
       <c r="O92" s="1"/>
@@ -3327,80 +3420,80 @@
     </row>
     <row r="93" spans="1:19">
       <c r="A93" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B93" t="s">
         <v>2</v>
       </c>
       <c r="C93" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93">
-        <v>6.7400000000000002E-2</v>
+        <v>4.2599999999999999E-2</v>
       </c>
       <c r="F93">
-        <v>3.2199999999999999E-2</v>
+        <v>2.06E-2</v>
       </c>
       <c r="G93" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H93">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="94" spans="1:19">
       <c r="A94" t="s">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c r="B94" t="s">
         <v>2</v>
       </c>
       <c r="C94" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>5.4899999999999997E-2</v>
+        <v>3.49E-2</v>
       </c>
       <c r="F94">
-        <v>2.7199999999999998E-2</v>
+        <v>1.67E-2</v>
       </c>
       <c r="G94" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H94">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:19">
       <c r="A95" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="B95" t="s">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95">
-        <v>4.2500000000000003E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="F95">
-        <v>2.2700000000000001E-2</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G95" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M95" s="1"/>
       <c r="O95" s="1"/>
@@ -3409,28 +3502,28 @@
     </row>
     <row r="96" spans="1:19">
       <c r="A96" t="s">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="B96" t="s">
         <v>2</v>
       </c>
       <c r="C96" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>7.0000000000000001E-3</v>
+        <v>4.4200000000000003E-2</v>
       </c>
       <c r="F96">
-        <v>3.3E-3</v>
+        <v>2.0899999999999998E-2</v>
       </c>
       <c r="G96" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M96" s="1"/>
       <c r="O96" s="1"/>
@@ -3439,106 +3532,106 @@
     </row>
     <row r="97" spans="1:19">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B97" t="s">
         <v>2</v>
       </c>
       <c r="C97" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>7.4999999999999997E-3</v>
+        <v>5.7700000000000001E-2</v>
       </c>
       <c r="F97">
-        <v>3.5000000000000001E-3</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="G97" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="98" spans="1:19">
       <c r="A98" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B98" t="s">
         <v>2</v>
       </c>
       <c r="C98" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>8.8000000000000005E-3</v>
+        <v>5.9900000000000002E-2</v>
       </c>
       <c r="F98">
-        <v>4.0000000000000001E-3</v>
+        <v>2.7799999999999998E-2</v>
       </c>
       <c r="G98" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="99" spans="1:19">
       <c r="A99" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B99" t="s">
         <v>2</v>
       </c>
       <c r="C99" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>1.0800000000000001E-2</v>
+        <v>4.9700000000000001E-2</v>
       </c>
       <c r="F99">
-        <v>5.0000000000000001E-3</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="G99" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="100" spans="1:19">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="B100" t="s">
         <v>2</v>
       </c>
       <c r="C100" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100">
-        <v>1.4999999999999999E-2</v>
+        <v>3.9199999999999999E-2</v>
       </c>
       <c r="F100">
-        <v>7.1000000000000004E-3</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="G100" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="M100" s="1"/>
       <c r="O100" s="1"/>
@@ -3547,85 +3640,53 @@
     </row>
     <row r="101" spans="1:19">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>157</v>
       </c>
       <c r="B101" t="s">
         <v>2</v>
       </c>
       <c r="C101" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>2.93E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="F101">
-        <v>1.41E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="G101" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:19">
-      <c r="A102" t="s">
-        <v>139</v>
-      </c>
-      <c r="B102" t="s">
-        <v>2</v>
-      </c>
-      <c r="C102" t="s">
-        <v>1</v>
-      </c>
-      <c r="D102">
-        <v>1</v>
-      </c>
-      <c r="E102">
-        <v>2.1100000000000001E-2</v>
-      </c>
-      <c r="F102">
-        <v>1.06E-2</v>
-      </c>
-      <c r="G102" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:19">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B103" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="C103" t="s">
-        <v>1</v>
-      </c>
-      <c r="D103">
-        <v>1</v>
-      </c>
-      <c r="E103">
-        <v>2.8400000000000002E-2</v>
-      </c>
-      <c r="F103">
-        <v>1.43E-2</v>
-      </c>
-      <c r="G103" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103">
-        <v>0.1</v>
+        <v>47</v>
+      </c>
+      <c r="D103" t="s">
+        <v>46</v>
+      </c>
+      <c r="E103" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="104" spans="1:19">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="B104" t="s">
         <v>2</v>
@@ -3637,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="E104">
-        <v>4.07E-2</v>
+        <v>3.44E-2</v>
       </c>
       <c r="F104">
-        <v>2.0299999999999999E-2</v>
+        <v>1.66E-2</v>
       </c>
       <c r="G104" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H104">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M104" s="1"/>
       <c r="O104" s="1"/>
@@ -3655,7 +3716,7 @@
     </row>
     <row r="105" spans="1:19">
       <c r="A105" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B105" t="s">
         <v>2</v>
@@ -3667,21 +3728,21 @@
         <v>1</v>
       </c>
       <c r="E105">
-        <v>5.0099999999999999E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="F105">
-        <v>2.5100000000000001E-2</v>
+        <v>2.07E-2</v>
       </c>
       <c r="G105" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H105">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="106" spans="1:19">
       <c r="A106" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B106" t="s">
         <v>2</v>
@@ -3693,21 +3754,21 @@
         <v>1</v>
       </c>
       <c r="E106">
-        <v>5.3199999999999997E-2</v>
+        <v>5.8099999999999999E-2</v>
       </c>
       <c r="F106">
-        <v>2.7E-2</v>
+        <v>2.7799999999999998E-2</v>
       </c>
       <c r="G106" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H106">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="107" spans="1:19">
       <c r="A107" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B107" t="s">
         <v>2</v>
@@ -3719,21 +3780,21 @@
         <v>1</v>
       </c>
       <c r="E107">
-        <v>4.3799999999999999E-2</v>
+        <v>6.7400000000000002E-2</v>
       </c>
       <c r="F107">
-        <v>2.3400000000000001E-2</v>
+        <v>3.2199999999999999E-2</v>
       </c>
       <c r="G107" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H107">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="108" spans="1:19">
       <c r="A108" t="s">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="B108" t="s">
         <v>2</v>
@@ -3745,16 +3806,16 @@
         <v>1</v>
       </c>
       <c r="E108">
-        <v>3.4599999999999999E-2</v>
+        <v>5.4899999999999997E-2</v>
       </c>
       <c r="F108">
-        <v>1.6799999999999999E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="G108" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M108" s="1"/>
       <c r="O108" s="1"/>
@@ -3763,7 +3824,7 @@
     </row>
     <row r="109" spans="1:19">
       <c r="A109" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B109" t="s">
         <v>2</v>
@@ -3775,21 +3836,21 @@
         <v>1</v>
       </c>
       <c r="E109">
-        <v>4.2299999999999997E-2</v>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="F109">
-        <v>2.0500000000000001E-2</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="G109" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H109">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="110" spans="1:19">
       <c r="A110" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="B110" t="s">
         <v>2</v>
@@ -3801,21 +3862,21 @@
         <v>1</v>
       </c>
       <c r="E110">
-        <v>5.9400000000000001E-2</v>
+        <v>3.7100000000000001E-2</v>
       </c>
       <c r="F110">
-        <v>2.86E-2</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="G110" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H110">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:19">
       <c r="A111" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="B111" t="s">
         <v>2</v>
@@ -3827,21 +3888,21 @@
         <v>1</v>
       </c>
       <c r="E111">
-        <v>7.5800000000000006E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F111">
-        <v>3.6700000000000003E-2</v>
+        <v>3.3E-3</v>
       </c>
       <c r="G111" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H111">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:19">
       <c r="A112" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B112" t="s">
         <v>2</v>
@@ -3853,16 +3914,16 @@
         <v>1</v>
       </c>
       <c r="E112">
-        <v>6.6799999999999998E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="F112">
-        <v>3.32E-2</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G112" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H112">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="M112" s="1"/>
       <c r="O112" s="1"/>
@@ -3871,7 +3932,7 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B113" t="s">
         <v>2</v>
@@ -3883,47 +3944,47 @@
         <v>1</v>
       </c>
       <c r="E113">
-        <v>4.65E-2</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="F113">
-        <v>2.47E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="G113" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H113">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D114" s="3">
-        <v>1</v>
-      </c>
-      <c r="E114" s="3">
-        <v>3.2399999999999998E-2</v>
-      </c>
-      <c r="F114" s="3">
-        <v>1.54E-2</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>14</v>
+      <c r="A114" t="s">
+        <v>35</v>
+      </c>
+      <c r="B114" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="F114">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G114" t="s">
+        <v>32</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B115" t="s">
         <v>2</v>
@@ -3935,21 +3996,21 @@
         <v>1</v>
       </c>
       <c r="E115">
-        <v>4.1500000000000002E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="F115">
-        <v>2.0199999999999999E-2</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="G115" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H115">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B116" t="s">
         <v>2</v>
@@ -3961,21 +4022,21 @@
         <v>1</v>
       </c>
       <c r="E116">
-        <v>5.9799999999999999E-2</v>
+        <v>2.93E-2</v>
       </c>
       <c r="F116">
-        <v>2.8400000000000002E-2</v>
+        <v>1.41E-2</v>
       </c>
       <c r="G116" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H116">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="B117" t="s">
         <v>2</v>
@@ -3987,21 +4048,21 @@
         <v>1</v>
       </c>
       <c r="E117">
-        <v>7.6399999999999996E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="F117">
-        <v>3.6700000000000003E-2</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="G117" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H117">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="B118" t="s">
         <v>2</v>
@@ -4013,21 +4074,21 @@
         <v>1</v>
       </c>
       <c r="E118">
-        <v>6.7199999999999996E-2</v>
+        <v>2.1100000000000001E-2</v>
       </c>
       <c r="F118">
-        <v>3.32E-2</v>
+        <v>1.06E-2</v>
       </c>
       <c r="G118" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H118">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B119" t="s">
         <v>2</v>
@@ -4039,21 +4100,21 @@
         <v>1</v>
       </c>
       <c r="E119">
-        <v>4.7800000000000002E-2</v>
+        <v>2.8400000000000002E-2</v>
       </c>
       <c r="F119">
-        <v>2.4899999999999999E-2</v>
+        <v>1.43E-2</v>
       </c>
       <c r="G119" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H119">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="B120" t="s">
         <v>2</v>
@@ -4065,21 +4126,21 @@
         <v>1</v>
       </c>
       <c r="E120">
-        <v>9.4000000000000004E-3</v>
+        <v>4.07E-2</v>
       </c>
       <c r="F120">
-        <v>4.1000000000000003E-3</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="G120" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B121" t="s">
         <v>2</v>
@@ -4091,21 +4152,21 @@
         <v>1</v>
       </c>
       <c r="E121">
-        <v>2.0299999999999999E-2</v>
+        <v>5.0099999999999999E-2</v>
       </c>
       <c r="F121">
-        <v>9.1000000000000004E-3</v>
+        <v>2.5100000000000001E-2</v>
       </c>
       <c r="G121" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H121">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B122" t="s">
         <v>2</v>
@@ -4117,21 +4178,21 @@
         <v>1</v>
       </c>
       <c r="E122">
-        <v>4.0899999999999999E-2</v>
+        <v>5.3199999999999997E-2</v>
       </c>
       <c r="F122">
-        <v>1.9E-2</v>
+        <v>2.7E-2</v>
       </c>
       <c r="G122" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H122">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B123" t="s">
         <v>2</v>
@@ -4143,21 +4204,21 @@
         <v>1</v>
       </c>
       <c r="E123">
-        <v>5.9900000000000002E-2</v>
+        <v>4.3799999999999999E-2</v>
       </c>
       <c r="F123">
-        <v>2.9499999999999998E-2</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="G123" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H123">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="B124" t="s">
         <v>2</v>
@@ -4169,21 +4230,21 @@
         <v>1</v>
       </c>
       <c r="E124">
-        <v>5.6300000000000003E-2</v>
+        <v>3.7100000000000001E-2</v>
       </c>
       <c r="F124">
-        <v>2.8400000000000002E-2</v>
+        <v>2.0199999999999999E-2</v>
       </c>
       <c r="G124" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H124">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="B125" t="s">
         <v>2</v>
@@ -4195,21 +4256,21 @@
         <v>1</v>
       </c>
       <c r="E125">
-        <v>4.3799999999999999E-2</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="F125">
-        <v>2.3300000000000001E-2</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="G125" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H125">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="B126" t="s">
         <v>2</v>
@@ -4221,21 +4282,21 @@
         <v>1</v>
       </c>
       <c r="E126">
-        <v>2.29E-2</v>
+        <v>4.2299999999999997E-2</v>
       </c>
       <c r="F126">
-        <v>1.0800000000000001E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G126" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B127" t="s">
         <v>2</v>
@@ -4247,21 +4308,21 @@
         <v>1</v>
       </c>
       <c r="E127">
-        <v>2.8799999999999999E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="F127">
-        <v>1.34E-2</v>
+        <v>2.86E-2</v>
       </c>
       <c r="G127" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H127">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B128" t="s">
         <v>2</v>
@@ -4273,21 +4334,21 @@
         <v>1</v>
       </c>
       <c r="E128">
-        <v>4.7399999999999998E-2</v>
+        <v>7.5800000000000006E-2</v>
       </c>
       <c r="F128">
-        <v>2.2100000000000002E-2</v>
+        <v>3.6700000000000003E-2</v>
       </c>
       <c r="G128" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H128">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B129" t="s">
         <v>2</v>
@@ -4299,21 +4360,21 @@
         <v>1</v>
       </c>
       <c r="E129">
-        <v>6.3299999999999995E-2</v>
+        <v>6.6799999999999998E-2</v>
       </c>
       <c r="F129">
-        <v>3.0300000000000001E-2</v>
+        <v>3.32E-2</v>
       </c>
       <c r="G129" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H129">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B130" t="s">
         <v>2</v>
@@ -4325,42 +4386,588 @@
         <v>1</v>
       </c>
       <c r="E130">
-        <v>6.0699999999999997E-2</v>
+        <v>4.65E-2</v>
       </c>
       <c r="F130">
-        <v>3.0499999999999999E-2</v>
+        <v>2.47E-2</v>
       </c>
       <c r="G130" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H130">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
+        <v>161</v>
+      </c>
+      <c r="B131" t="s">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="F131">
+        <v>2.01E-2</v>
+      </c>
+      <c r="G131" t="s">
+        <v>20</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D132" s="3">
+        <v>1</v>
+      </c>
+      <c r="E132" s="3">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="F132" s="3">
+        <v>1.54E-2</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133" t="s">
+        <v>2</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="F133">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="G133" t="s">
+        <v>14</v>
+      </c>
+      <c r="H133">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>18</v>
+      </c>
+      <c r="B134" t="s">
+        <v>2</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="F134">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="G134" t="s">
+        <v>14</v>
+      </c>
+      <c r="H134">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>17</v>
+      </c>
+      <c r="B135" t="s">
+        <v>2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>7.6399999999999996E-2</v>
+      </c>
+      <c r="F135">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="G135" t="s">
+        <v>14</v>
+      </c>
+      <c r="H135">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>16</v>
+      </c>
+      <c r="B136" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>6.7199999999999996E-2</v>
+      </c>
+      <c r="F136">
+        <v>3.32E-2</v>
+      </c>
+      <c r="G136" t="s">
+        <v>14</v>
+      </c>
+      <c r="H136">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>2</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="F137">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="G137" t="s">
+        <v>14</v>
+      </c>
+      <c r="H137">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>162</v>
+      </c>
+      <c r="B138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F138">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="G138" t="s">
+        <v>14</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139" t="s">
+        <v>2</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="F139">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="G139" t="s">
+        <v>8</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>13</v>
+      </c>
+      <c r="B140" t="s">
+        <v>2</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="F140">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="G140" t="s">
+        <v>8</v>
+      </c>
+      <c r="H140">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>12</v>
+      </c>
+      <c r="B141" t="s">
+        <v>2</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1</v>
+      </c>
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="E141">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="F141">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G141" t="s">
+        <v>8</v>
+      </c>
+      <c r="H141">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>11</v>
+      </c>
+      <c r="B142" t="s">
+        <v>2</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="F142">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="G142" t="s">
+        <v>8</v>
+      </c>
+      <c r="H142">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
+        <v>10</v>
+      </c>
+      <c r="B143" t="s">
+        <v>2</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="F143">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="G143" t="s">
+        <v>8</v>
+      </c>
+      <c r="H143">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144" t="s">
+        <v>2</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1</v>
+      </c>
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144">
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="F144">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="G144" t="s">
+        <v>8</v>
+      </c>
+      <c r="H144">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
+        <v>163</v>
+      </c>
+      <c r="B145" t="s">
+        <v>2</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1</v>
+      </c>
+      <c r="D145">
+        <v>1</v>
+      </c>
+      <c r="E145">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="F145">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="G145" t="s">
+        <v>8</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>143</v>
+      </c>
+      <c r="B146" t="s">
+        <v>2</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146">
+        <v>2.29E-2</v>
+      </c>
+      <c r="F146">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G146" t="s">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>7</v>
+      </c>
+      <c r="B147" t="s">
+        <v>2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1</v>
+      </c>
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="E147">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="F147">
+        <v>1.34E-2</v>
+      </c>
+      <c r="G147" t="s">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>6</v>
+      </c>
+      <c r="B148" t="s">
+        <v>2</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1</v>
+      </c>
+      <c r="D148">
+        <v>1</v>
+      </c>
+      <c r="E148">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="F148">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="G148" t="s">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>5</v>
+      </c>
+      <c r="B149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="E149">
+        <v>6.3299999999999995E-2</v>
+      </c>
+      <c r="F149">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="G149" t="s">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>4</v>
+      </c>
+      <c r="B150" t="s">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1</v>
+      </c>
+      <c r="D150">
+        <v>1</v>
+      </c>
+      <c r="E150">
+        <v>6.0699999999999997E-2</v>
+      </c>
+      <c r="F150">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="G150" t="s">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
         <v>3</v>
       </c>
-      <c r="B131" t="s">
-        <v>2</v>
-      </c>
-      <c r="C131" t="s">
-        <v>1</v>
-      </c>
-      <c r="D131">
-        <v>1</v>
-      </c>
-      <c r="E131">
+      <c r="B151" t="s">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="E151">
         <v>4.58E-2</v>
       </c>
-      <c r="F131">
+      <c r="F151">
         <v>2.4199999999999999E-2</v>
       </c>
-      <c r="G131" t="s">
+      <c r="G151" t="s">
         <v>0</v>
       </c>
-      <c r="H131">
+      <c r="H151">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>164</v>
+      </c>
+      <c r="B152" t="s">
+        <v>2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
+      </c>
+      <c r="E152">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="F152">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="G152" t="s">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
